--- a/03_Outputs/all/01_TablasDescriptivas/idx5_viviendas.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx5_viviendas.xlsx
@@ -462,7 +462,7 @@
         <v>124</v>
       </c>
       <c r="C5">
-        <v>-9.850838915034158</v>
+        <v>-9.85083891503416</v>
       </c>
       <c r="D5">
         <v>15.43012327600922</v>
@@ -509,7 +509,7 @@
         <v>-0.5460616906107807</v>
       </c>
       <c r="D7">
-        <v>0.8425997122213289</v>
+        <v>0.8425997122213283</v>
       </c>
       <c r="E7">
         <v>-4.1025641025641</v>
